--- a/templates/입고주문-AVNET-임포트.xlsx
+++ b/templates/입고주문-AVNET-임포트.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10312"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10208"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6590004D-8A4B-FE48-A989-72C0F2188246}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D39FEB52-E432-1447-9F8F-65635AC2BB37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="33080" yWindow="2720" windowWidth="27620" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="25">
   <si>
     <t>입고요청일</t>
   </si>
@@ -130,14 +130,6 @@
   </si>
   <si>
     <t>AVNET</t>
-  </si>
-  <si>
-    <t>Date Code</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>B/L</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>INVOICE</t>
@@ -189,15 +181,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>2140</t>
-  </si>
-  <si>
-    <t>2142</t>
-  </si>
-  <si>
-    <t>2152</t>
-  </si>
-  <si>
     <t>M20260323</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -212,6 +195,18 @@
   <si>
     <t>2026-03-23</t>
     <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>유효기간</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2027-12-31</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>입고요청번호</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -323,7 +318,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
@@ -347,6 +342,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -695,6 +693,7 @@
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="8" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.5" style="1"/>
+    <col min="12" max="12" width="14.5" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="18">
@@ -708,7 +707,7 @@
         <v>4</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E1" s="7" t="s">
         <v>0</v>
@@ -723,7 +722,7 @@
         <v>9</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J1" s="7" t="s">
         <v>6</v>
@@ -731,26 +730,26 @@
       <c r="K1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="9" t="s">
-        <v>13</v>
+      <c r="L1" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="M1" s="7" t="s">
         <v>8</v>
       </c>
       <c r="N1" s="7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O1" s="7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="P1" s="9" t="s">
         <v>10</v>
       </c>
       <c r="Q1" s="9" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="R1" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -764,10 +763,10 @@
         <v>12</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F2" s="3">
         <v>1</v>
@@ -785,8 +784,8 @@
       <c r="K2" s="6">
         <v>17000</v>
       </c>
-      <c r="L2" s="5" t="s">
-        <v>20</v>
+      <c r="L2" s="11" t="s">
+        <v>23</v>
       </c>
       <c r="M2" s="5"/>
       <c r="N2" s="3"/>
@@ -806,16 +805,16 @@
         <v>12</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F3" s="3">
         <v>1</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H3" s="10">
         <v>2026032301</v>
@@ -827,8 +826,8 @@
       <c r="K3" s="6">
         <v>17000</v>
       </c>
-      <c r="L3" s="5" t="s">
-        <v>21</v>
+      <c r="L3" s="11" t="s">
+        <v>23</v>
       </c>
       <c r="M3" s="5"/>
       <c r="N3" s="3"/>
@@ -848,16 +847,16 @@
         <v>12</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F4" s="3">
         <v>1</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H4" s="10">
         <v>2026032301</v>
@@ -869,8 +868,8 @@
       <c r="K4" s="6">
         <v>40000</v>
       </c>
-      <c r="L4" s="5" t="s">
-        <v>22</v>
+      <c r="L4" s="11" t="s">
+        <v>23</v>
       </c>
       <c r="M4" s="5"/>
       <c r="N4" s="3"/>
